--- a/public/warehouse.xlsx
+++ b/public/warehouse.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://valcolattesrl-my.sharepoint.com/personal/macellarit_valcolatte_it/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://valcolattesrl-my.sharepoint.com/personal/macellarit_valcolatte_it/Documents/Desktop/warehouse-app/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ECFA101-5E3D-4628-AC0A-10C091EE9BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{6ECFA101-5E3D-4628-AC0A-10C091EE9BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF28E95B-EB9B-44A4-9592-5BEB472C0711}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,6 +454,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -486,7 +493,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -517,10 +524,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -537,7 +544,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
